--- a/seo-geo/tracking/issue-tracker-for-gsheet-import.xlsx
+++ b/seo-geo/tracking/issue-tracker-for-gsheet-import.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Issues" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Issues'!$A$1:$M$252</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Issues'!$A$1:$M$253</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,15 +28,37 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -53,18 +75,32 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -427,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M252"/>
+  <dimension ref="A1:M253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -440,7 +476,7 @@
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="36" customWidth="1" min="11" max="11"/>
     <col width="30" customWidth="1" min="12" max="12"/>
     <col width="30" customWidth="1" min="13" max="13"/>
   </cols>
@@ -531,7 +567,7 @@
           <t>Deleted article: Streamlining Logistics for Scalable Amazon Success</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/streamlining-logistics-for-scalable-amazon-success/</t>
         </is>
@@ -561,9 +597,9 @@
           <t>new</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Open, urgent (confirmed again 2026-09-14: article still not restored, 5 days after it was found deleted)</t>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>Open, urgent (confirmed again 2026-09-16: article still not restored, 7 days after it was found deleted)</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr"/>
@@ -588,7 +624,7 @@
           <t>All 86 crawled pages</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/</t>
         </is>
@@ -641,7 +677,7 @@
           <t>All 86 crawled pages</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/</t>
         </is>
@@ -694,7 +730,7 @@
           <t>All 86 crawled pages</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/</t>
         </is>
@@ -747,7 +783,7 @@
           <t>All 86 crawled pages</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/</t>
         </is>
@@ -800,7 +836,7 @@
           <t>All 86 crawled pages</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/</t>
         </is>
@@ -853,7 +889,7 @@
           <t>Homepage</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/</t>
         </is>
@@ -906,7 +942,7 @@
           <t>Category archive: uncategorized</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/category/uncategorized/</t>
         </is>
@@ -936,7 +972,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -963,7 +999,7 @@
           <t>Category archive: grocery</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/category/grocery/</t>
         </is>
@@ -993,7 +1029,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -1020,7 +1056,7 @@
           <t>Category archive: apparel</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/category/apparel/</t>
         </is>
@@ -1050,7 +1086,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -1077,7 +1113,7 @@
           <t>Category archive: health-household</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/category/health-household/</t>
         </is>
@@ -1107,7 +1143,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -1134,7 +1170,7 @@
           <t>Category archive: beauty-personal-care</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/category/beauty-personal-care/</t>
         </is>
@@ -1164,7 +1200,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -1191,7 +1227,7 @@
           <t>Category archive: amazon-agency</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/category/amazon-agency/</t>
         </is>
@@ -1221,7 +1257,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -1248,7 +1284,7 @@
           <t>Category archive: amazon-advertising</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/category/amazon-advertising/</t>
         </is>
@@ -1278,7 +1314,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -1305,7 +1341,7 @@
           <t>Tag archive: bags</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/tag/bags/</t>
         </is>
@@ -1335,7 +1371,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -1362,7 +1398,7 @@
           <t>Tag archive: subscribe-and-save</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/tag/subscribe-and-save/</t>
         </is>
@@ -1392,7 +1428,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -1419,7 +1455,7 @@
           <t>Project category archive: apparel</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/project_category/apparel/</t>
         </is>
@@ -1449,7 +1485,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -1476,7 +1512,7 @@
           <t>Project category archive: automotive</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/project_category/automotive/</t>
         </is>
@@ -1506,7 +1542,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -1533,7 +1569,7 @@
           <t>Project category archive: beauty-cosmetics</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/project_category/beauty-cosmetics/</t>
         </is>
@@ -1563,7 +1599,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -1590,7 +1626,7 @@
           <t>Project category archive: food</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/project_category/food/</t>
         </is>
@@ -1620,7 +1656,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -1647,7 +1683,7 @@
           <t>Project category archive: furniture</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/project_category/furniture/</t>
         </is>
@@ -1677,7 +1713,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -1704,7 +1740,7 @@
           <t>Project category archive: homewares</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/project_category/homewares/</t>
         </is>
@@ -1734,7 +1770,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -1761,7 +1797,7 @@
           <t>Project category archive: outdoors</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/project_category/outdoors/</t>
         </is>
@@ -1791,7 +1827,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="K24" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -1818,7 +1854,7 @@
           <t>Project category archive: pet</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/project_category/pet/</t>
         </is>
@@ -1848,7 +1884,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -1875,7 +1911,7 @@
           <t>Project category archive: tech-accessories</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/project_category/tech-accessories/</t>
         </is>
@@ -1905,7 +1941,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="K26" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -1932,7 +1968,7 @@
           <t>Project category archive: vitamins-supplements</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/project_category/vitamins-supplements/</t>
         </is>
@@ -1962,7 +1998,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -1989,7 +2025,7 @@
           <t>Project post-type archive</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/project/</t>
         </is>
@@ -2042,7 +2078,7 @@
           <t>Author archive: 7121525_u8r6t1</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/author/7121525_u8r6t1/</t>
         </is>
@@ -2072,7 +2108,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="K29" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -2099,7 +2135,7 @@
           <t>Author archive: Albert Scott</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/author/albertllc/</t>
         </is>
@@ -2129,7 +2165,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="K30" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -2156,7 +2192,7 @@
           <t>Author archive: Hannah Kaufman</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/author/hannah-kaufman/</t>
         </is>
@@ -2186,7 +2222,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="K31" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -2213,7 +2249,7 @@
           <t>Author archive: Hashsalacop</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/author/hashsalacop/</t>
         </is>
@@ -2243,7 +2279,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="K32" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -2270,7 +2306,7 @@
           <t>1,075 media attachment pages (sample of 2 checked)</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/wp-content/uploads/2026/08/0x0.webp</t>
         </is>
@@ -2323,7 +2359,7 @@
           <t>Dead URL: /marketing-management/</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/marketing-management/</t>
         </is>
@@ -2353,7 +2389,7 @@
           <t>R5</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="K34" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -2380,7 +2416,7 @@
           <t>Dead URL: /privacy-policy-2/</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/privacy-policy-2/</t>
         </is>
@@ -2410,7 +2446,7 @@
           <t>R5</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="K35" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -2437,7 +2473,7 @@
           <t>Missing page: /blog/</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/</t>
         </is>
@@ -2467,7 +2503,7 @@
           <t>R19</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="K36" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -2494,7 +2530,7 @@
           <t>Homepage</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/</t>
         </is>
@@ -2524,7 +2560,7 @@
           <t>R2</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="K37" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -2551,7 +2587,7 @@
           <t>Homepage</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/</t>
         </is>
@@ -2581,9 +2617,9 @@
           <t>R2</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>Done (verified 2026-09-14)</t>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>REOPENED (verified 2026-09-16: the homepage still links to https://www.albertscott.com/marketing-division/, which 301s to /marketing-devision/, confirmed by fetching the live homepage HTML directly. Not a measurement error this time; a plain absolute link on the page.)</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr"/>
@@ -2608,7 +2644,7 @@
           <t>Homepage</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/</t>
         </is>
@@ -2638,9 +2674,9 @@
           <t>R2</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>Done (verified 2026-09-14)</t>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>REOPENED (verified 2026-09-16: the homepage's "Explore Logistics" button in the divisions accordion section links to /logistics-division-2/ (relative href), confirmed by fetching the live homepage HTML directly. A correct absolute link to /logistics-division/ also exists elsewhere on the page, so this looks like a second button using the old URL, not the original one being un-fixed.)</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr"/>
@@ -2665,7 +2701,7 @@
           <t>Portfolio gallery page</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/listings-portfolio-gallery/</t>
         </is>
@@ -2718,7 +2754,7 @@
           <t>Marketing division page</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/marketing-devision/</t>
         </is>
@@ -2771,7 +2807,7 @@
           <t>Marketing division page (duplicate)</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/marketing-division-2/</t>
         </is>
@@ -2801,9 +2837,9 @@
           <t>R2</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>Done (verified 2026-09-14: the source page /marketing-division-2/ itself now 301s, confirmed via a direct HTTP check; an earlier automated pass misread this because a browser-based crawl follows redirects and reports the destination page instead of the redirect)</t>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-16: source page no longer exists as a separate page, moot)</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr"/>
@@ -2828,7 +2864,7 @@
           <t>Homepage</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/</t>
         </is>
@@ -2881,7 +2917,7 @@
           <t>Homepage</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/</t>
         </is>
@@ -2934,7 +2970,7 @@
           <t>Homepage</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/</t>
         </is>
@@ -2987,7 +3023,7 @@
           <t>Homepage</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/</t>
         </is>
@@ -3040,7 +3076,7 @@
           <t>Homepage</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/</t>
         </is>
@@ -3093,7 +3129,7 @@
           <t>Homepage</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/</t>
         </is>
@@ -3146,7 +3182,7 @@
           <t>Homepage</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/</t>
         </is>
@@ -3199,7 +3235,7 @@
           <t>About page</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E50" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/about-us/</t>
         </is>
@@ -3252,7 +3288,7 @@
           <t>About page</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/about-us/</t>
         </is>
@@ -3305,7 +3341,7 @@
           <t>About page</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E52" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/about-us/</t>
         </is>
@@ -3358,7 +3394,7 @@
           <t>About page</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/about-us/</t>
         </is>
@@ -3411,7 +3447,7 @@
           <t>About page</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E54" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/about-us/</t>
         </is>
@@ -3464,7 +3500,7 @@
           <t>About page</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/about-us/</t>
         </is>
@@ -3517,7 +3553,7 @@
           <t>About page</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E56" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/about-us/</t>
         </is>
@@ -3570,7 +3606,7 @@
           <t>Listing division page</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/listing-division/</t>
         </is>
@@ -3623,7 +3659,7 @@
           <t>Listing division page</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E58" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/listing-division/</t>
         </is>
@@ -3676,7 +3712,7 @@
           <t>Listing division page</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/listing-division/</t>
         </is>
@@ -3729,7 +3765,7 @@
           <t>Listing division page</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E60" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/listing-division/</t>
         </is>
@@ -3782,7 +3818,7 @@
           <t>Listing division page</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/listing-division/</t>
         </is>
@@ -3835,7 +3871,7 @@
           <t>Marketing division page</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E62" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/marketing-devision/</t>
         </is>
@@ -3888,7 +3924,7 @@
           <t>Marketing division page</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/marketing-devision/</t>
         </is>
@@ -3941,7 +3977,7 @@
           <t>Marketing division page</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E64" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/marketing-devision/</t>
         </is>
@@ -3971,7 +4007,11 @@
           <t>R8</t>
         </is>
       </c>
-      <c r="K64" s="2" t="inlineStr"/>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-16)</t>
+        </is>
+      </c>
       <c r="L64" s="2" t="inlineStr"/>
       <c r="M64" s="2" t="inlineStr"/>
     </row>
@@ -3994,7 +4034,7 @@
           <t>Marketing division page</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E65" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/marketing-devision/</t>
         </is>
@@ -4047,7 +4087,7 @@
           <t>Marketing division page</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E66" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/marketing-devision/</t>
         </is>
@@ -4100,7 +4140,7 @@
           <t>Marketing division page</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/marketing-devision/</t>
         </is>
@@ -4153,7 +4193,7 @@
           <t>Marketing division page</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E68" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/marketing-devision/</t>
         </is>
@@ -4206,7 +4246,7 @@
           <t>Marketing division page</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/marketing-devision/</t>
         </is>
@@ -4259,7 +4299,7 @@
           <t>Marketing division page</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E70" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/marketing-devision/</t>
         </is>
@@ -4312,7 +4352,7 @@
           <t>Retail division page</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E71" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/retail-division/</t>
         </is>
@@ -4365,7 +4405,7 @@
           <t>Retail division page</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E72" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/retail-division/</t>
         </is>
@@ -4418,7 +4458,7 @@
           <t>Retail division page</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E73" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/retail-division/</t>
         </is>
@@ -4471,7 +4511,7 @@
           <t>Retail division page</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E74" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/retail-division/</t>
         </is>
@@ -4524,7 +4564,7 @@
           <t>Retail division page</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E75" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/retail-division/</t>
         </is>
@@ -4577,7 +4617,7 @@
           <t>Logistics division page</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E76" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/logistics-division/</t>
         </is>
@@ -4630,7 +4670,7 @@
           <t>Logistics division page</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E77" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/logistics-division/</t>
         </is>
@@ -4683,7 +4723,7 @@
           <t>Logistics division page</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E78" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/logistics-division/</t>
         </is>
@@ -4736,7 +4776,7 @@
           <t>Logistics division page</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E79" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/logistics-division/</t>
         </is>
@@ -4789,7 +4829,7 @@
           <t>Logistics division page</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E80" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/logistics-division/</t>
         </is>
@@ -4842,7 +4882,7 @@
           <t>DSP page</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E81" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/dsp/</t>
         </is>
@@ -4895,7 +4935,7 @@
           <t>DSP page</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E82" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/dsp/</t>
         </is>
@@ -4948,7 +4988,7 @@
           <t>DSP page</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E83" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/dsp/</t>
         </is>
@@ -5001,7 +5041,7 @@
           <t>DSP page</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E84" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/dsp/</t>
         </is>
@@ -5031,7 +5071,7 @@
           <t>R18</t>
         </is>
       </c>
-      <c r="K84" s="2" t="inlineStr">
+      <c r="K84" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -5058,7 +5098,7 @@
           <t>DSP page</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E85" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/dsp/</t>
         </is>
@@ -5111,7 +5151,7 @@
           <t>DSP page</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E86" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/dsp/</t>
         </is>
@@ -5164,7 +5204,7 @@
           <t>Case studies page</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E87" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/case-studies/</t>
         </is>
@@ -5217,7 +5257,7 @@
           <t>Case studies page</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E88" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/case-studies/</t>
         </is>
@@ -5270,7 +5310,7 @@
           <t>Case studies page</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E89" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/case-studies/</t>
         </is>
@@ -5323,7 +5363,7 @@
           <t>Case studies page</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E90" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/case-studies/</t>
         </is>
@@ -5376,7 +5416,7 @@
           <t>Case study: BeYoutiful</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E91" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/case-studies/beyoutiful/</t>
         </is>
@@ -5429,7 +5469,7 @@
           <t>Case study: BeYoutiful</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E92" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/case-studies/beyoutiful/</t>
         </is>
@@ -5482,7 +5522,7 @@
           <t>Case study: BeYoutiful</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E93" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/case-studies/beyoutiful/</t>
         </is>
@@ -5535,7 +5575,7 @@
           <t>Case study: BeYoutiful</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E94" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/case-studies/beyoutiful/</t>
         </is>
@@ -5588,7 +5628,7 @@
           <t>Case study: BeYoutiful</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E95" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/case-studies/beyoutiful/</t>
         </is>
@@ -5618,7 +5658,7 @@
           <t>R18</t>
         </is>
       </c>
-      <c r="K95" s="2" t="inlineStr">
+      <c r="K95" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -5645,7 +5685,7 @@
           <t>Case study: BeYoutiful</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E96" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/case-studies/beyoutiful/</t>
         </is>
@@ -5698,7 +5738,7 @@
           <t>Case study: BeYoutiful</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E97" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/case-studies/beyoutiful/</t>
         </is>
@@ -5751,7 +5791,7 @@
           <t>Case study: Atlas Olive Oils</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E98" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/case-studies/atlas-olive-oils/</t>
         </is>
@@ -5804,7 +5844,7 @@
           <t>Case study: Atlas Olive Oils</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E99" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/case-studies/atlas-olive-oils/</t>
         </is>
@@ -5834,7 +5874,11 @@
           <t>R8</t>
         </is>
       </c>
-      <c r="K99" s="2" t="inlineStr"/>
+      <c r="K99" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-16)</t>
+        </is>
+      </c>
       <c r="L99" s="2" t="inlineStr"/>
       <c r="M99" s="2" t="inlineStr"/>
     </row>
@@ -5857,7 +5901,7 @@
           <t>Case study: Atlas Olive Oils</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E100" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/case-studies/atlas-olive-oils/</t>
         </is>
@@ -5910,7 +5954,7 @@
           <t>Case study: Atlas Olive Oils</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E101" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/case-studies/atlas-olive-oils/</t>
         </is>
@@ -5963,7 +6007,7 @@
           <t>Case study: Atlas Olive Oils</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E102" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/case-studies/atlas-olive-oils/</t>
         </is>
@@ -5993,7 +6037,7 @@
           <t>R18</t>
         </is>
       </c>
-      <c r="K102" s="2" t="inlineStr">
+      <c r="K102" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -6020,7 +6064,7 @@
           <t>Case study: Atlas Olive Oils</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E103" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/case-studies/atlas-olive-oils/</t>
         </is>
@@ -6073,7 +6117,7 @@
           <t>Case study: Atlas Olive Oils</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E104" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/case-studies/atlas-olive-oils/</t>
         </is>
@@ -6126,7 +6170,7 @@
           <t>Case study: Mouthwatchers (noindexed)</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E105" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/case-studies/mouthwatchers/</t>
         </is>
@@ -6179,7 +6223,7 @@
           <t>Case study: Mouthwatchers (noindexed)</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E106" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/case-studies/mouthwatchers/</t>
         </is>
@@ -6232,7 +6276,7 @@
           <t>Case study: Mouthwatchers (noindexed)</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E107" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/case-studies/mouthwatchers/</t>
         </is>
@@ -6285,7 +6329,7 @@
           <t>Case study: Mouthwatchers (noindexed)</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E108" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/case-studies/mouthwatchers/</t>
         </is>
@@ -6315,7 +6359,7 @@
           <t>R18</t>
         </is>
       </c>
-      <c r="K108" s="2" t="inlineStr">
+      <c r="K108" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -6342,7 +6386,7 @@
           <t>Case study: Mouthwatchers (noindexed)</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E109" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/case-studies/mouthwatchers/</t>
         </is>
@@ -6395,7 +6439,7 @@
           <t>Case study: Mouthwatchers (noindexed)</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E110" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/case-studies/mouthwatchers/</t>
         </is>
@@ -6448,7 +6492,7 @@
           <t>Case study: Mouthwatchers (noindexed)</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E111" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/case-studies/mouthwatchers/</t>
         </is>
@@ -6501,7 +6545,7 @@
           <t>Portfolio gallery page</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E112" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/listings-portfolio-gallery/</t>
         </is>
@@ -6554,7 +6598,7 @@
           <t>Portfolio gallery page</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E113" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/listings-portfolio-gallery/</t>
         </is>
@@ -6607,7 +6651,7 @@
           <t>Portfolio gallery page</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E114" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/listings-portfolio-gallery/</t>
         </is>
@@ -6660,7 +6704,7 @@
           <t>Portfolio gallery page</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E115" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/listings-portfolio-gallery/</t>
         </is>
@@ -6713,7 +6757,7 @@
           <t>Portfolio gallery page</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E116" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/listings-portfolio-gallery/</t>
         </is>
@@ -6766,7 +6810,7 @@
           <t>Portfolio gallery page</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E117" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/listings-portfolio-gallery/</t>
         </is>
@@ -6819,7 +6863,7 @@
           <t>Newsroom page</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E118" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/newsroom/</t>
         </is>
@@ -6872,7 +6916,7 @@
           <t>Newsroom page</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E119" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/newsroom/</t>
         </is>
@@ -6925,7 +6969,7 @@
           <t>Newsroom page</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E120" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/newsroom/</t>
         </is>
@@ -6978,7 +7022,7 @@
           <t>Newsroom page</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E121" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/newsroom/</t>
         </is>
@@ -7031,7 +7075,7 @@
           <t>University page</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E122" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/albert-scott-university/</t>
         </is>
@@ -7084,7 +7128,7 @@
           <t>University page</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E123" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/albert-scott-university/</t>
         </is>
@@ -7137,7 +7181,7 @@
           <t>University page</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E124" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/albert-scott-university/</t>
         </is>
@@ -7190,7 +7234,7 @@
           <t>University page</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E125" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/albert-scott-university/</t>
         </is>
@@ -7243,7 +7287,7 @@
           <t>University page</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E126" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/albert-scott-university/</t>
         </is>
@@ -7296,7 +7340,7 @@
           <t>Contact page</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E127" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/contact-us/</t>
         </is>
@@ -7349,7 +7393,7 @@
           <t>Contact page</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E128" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/contact-us/</t>
         </is>
@@ -7402,7 +7446,7 @@
           <t>Contact page</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E129" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/contact-us/</t>
         </is>
@@ -7455,7 +7499,7 @@
           <t>Contact page</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E130" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/contact-us/</t>
         </is>
@@ -7508,7 +7552,7 @@
           <t>Contact page</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E131" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/contact-us/</t>
         </is>
@@ -7561,7 +7605,7 @@
           <t>Contact page</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E132" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/contact-us/</t>
         </is>
@@ -7614,7 +7658,7 @@
           <t>Book a call page</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E133" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/book-a-call/</t>
         </is>
@@ -7667,7 +7711,7 @@
           <t>Book a call page</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E134" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/book-a-call/</t>
         </is>
@@ -7720,7 +7764,7 @@
           <t>Book a call page</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E135" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/book-a-call/</t>
         </is>
@@ -7773,7 +7817,7 @@
           <t>Book a call page</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E136" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/book-a-call/</t>
         </is>
@@ -7826,7 +7870,7 @@
           <t>Book a call page</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E137" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/book-a-call/</t>
         </is>
@@ -7879,7 +7923,7 @@
           <t>Book a call page</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E138" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/book-a-call/</t>
         </is>
@@ -7932,7 +7976,7 @@
           <t>Book a call page</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E139" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/book-a-call/</t>
         </is>
@@ -7985,7 +8029,7 @@
           <t>Book a call page</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E140" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/book-a-call/</t>
         </is>
@@ -8038,7 +8082,7 @@
           <t>Location page</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E141" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/our-location/</t>
         </is>
@@ -8091,7 +8135,7 @@
           <t>Location page</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E142" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/our-location/</t>
         </is>
@@ -8144,7 +8188,7 @@
           <t>Location page</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E143" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/our-location/</t>
         </is>
@@ -8197,7 +8241,7 @@
           <t>Location page</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E144" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/our-location/</t>
         </is>
@@ -8250,7 +8294,7 @@
           <t>Location page</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E145" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/our-location/</t>
         </is>
@@ -8303,7 +8347,7 @@
           <t>Location page</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E146" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/our-location/</t>
         </is>
@@ -8356,7 +8400,7 @@
           <t>Location page</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E147" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/our-location/</t>
         </is>
@@ -8409,7 +8453,7 @@
           <t>Location page</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E148" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/our-location/</t>
         </is>
@@ -8462,7 +8506,7 @@
           <t>Homepage</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E149" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/</t>
         </is>
@@ -8515,7 +8559,7 @@
           <t>Homepage</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E150" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/</t>
         </is>
@@ -8568,7 +8612,7 @@
           <t>Homepage</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E151" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/</t>
         </is>
@@ -8621,7 +8665,7 @@
           <t>Marketing division page</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E152" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/marketing-devision/</t>
         </is>
@@ -8674,7 +8718,7 @@
           <t>DSP page</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E153" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/dsp/</t>
         </is>
@@ -8727,7 +8771,7 @@
           <t>Contact page</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E154" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/contact-us/</t>
         </is>
@@ -8757,7 +8801,7 @@
           <t>R20</t>
         </is>
       </c>
-      <c r="K154" s="2" t="inlineStr">
+      <c r="K154" s="6" t="inlineStr">
         <is>
           <t>In progress (verified 2026-09-14: book-a-call now noindexed; lets-talk now redirects to contact-us)</t>
         </is>
@@ -8784,7 +8828,7 @@
           <t>Location page</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E155" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/our-location/</t>
         </is>
@@ -8837,7 +8881,7 @@
           <t>Newsroom page</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E156" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/newsroom/</t>
         </is>
@@ -8890,7 +8934,7 @@
           <t>University page</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E157" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/albert-scott-university/</t>
         </is>
@@ -8920,7 +8964,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K157" s="2" t="inlineStr">
+      <c r="K157" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -8947,7 +8991,7 @@
           <t>Portfolio gallery page</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E158" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/listings-portfolio-gallery/</t>
         </is>
@@ -9000,7 +9044,7 @@
           <t>Case studies page</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E159" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/case-studies/</t>
         </is>
@@ -9053,7 +9097,7 @@
           <t>Project: Superior Trading</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E160" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/project/superior-trading/</t>
         </is>
@@ -9106,7 +9150,7 @@
           <t>Project: Vianney</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E161" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/project/vianney/</t>
         </is>
@@ -9159,7 +9203,7 @@
           <t>Project: Verve Culture</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E162" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/project/verve-culture/</t>
         </is>
@@ -9212,7 +9256,7 @@
           <t>Project: The Matzo Project</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E163" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/project/the-matzo-project/</t>
         </is>
@@ -9265,7 +9309,7 @@
           <t>Project: Sunshine Nuts</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E164" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/project/sunshine-nuts/</t>
         </is>
@@ -9318,7 +9362,7 @@
           <t>Project: Snail Care</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E165" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/project/snail-care/</t>
         </is>
@@ -9371,7 +9415,7 @@
           <t>Project: Rufus Teague</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E166" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/project/rufus-teague/</t>
         </is>
@@ -9424,7 +9468,7 @@
           <t>Project: Renew RX</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E167" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/project/renew-rx/</t>
         </is>
@@ -9477,7 +9521,7 @@
           <t>Project: Simple Solution</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E168" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/project/simple-solution/</t>
         </is>
@@ -9530,7 +9574,7 @@
           <t>Project: OUT!</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E169" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/project/out/</t>
         </is>
@@ -9583,7 +9627,7 @@
           <t>Project: National Public Seatinf (slug misspells "seating")</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E170" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/project/national-public-seatinf/</t>
         </is>
@@ -9636,7 +9680,7 @@
           <t>Project: Nora</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E171" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/project/nora/</t>
         </is>
@@ -9689,7 +9733,7 @@
           <t>Project: Kagi</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E172" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/project/kagi/</t>
         </is>
@@ -9742,7 +9786,7 @@
           <t>Project: It's Just Smart</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E173" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/project/its-just-smart/</t>
         </is>
@@ -9795,7 +9839,7 @@
           <t>Project: Magmod</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E174" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/project/magmod/</t>
         </is>
@@ -9848,7 +9892,7 @@
           <t>Project: HYP</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E175" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/project/hyp/</t>
         </is>
@@ -9901,7 +9945,7 @@
           <t>Project: Human Beanz</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E176" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/project/human-beanz/</t>
         </is>
@@ -9954,7 +9998,7 @@
           <t>Project: Healthy Heist</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E177" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/project/healthy-heist/</t>
         </is>
@@ -10007,7 +10051,7 @@
           <t>Project: Mannol</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E178" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/project/mannol/</t>
         </is>
@@ -10060,7 +10104,7 @@
           <t>Project: Guylian</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E179" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/project/guylian/</t>
         </is>
@@ -10113,7 +10157,7 @@
           <t>Project: Great Western Foods</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E180" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/project/great-western-foods/</t>
         </is>
@@ -10166,7 +10210,7 @@
           <t>Project: Bluestem Botanicals</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E181" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/project/3835/</t>
         </is>
@@ -10219,7 +10263,7 @@
           <t>Project: Blue Chill</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E182" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/project/blue-chill/</t>
         </is>
@@ -10272,7 +10316,7 @@
           <t>Project: National Public Seatinf</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E183" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/project/national-public-seatinf/</t>
         </is>
@@ -10325,7 +10369,7 @@
           <t>Post: Mouthwatchers</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E184" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/mouthwatchers/</t>
         </is>
@@ -10378,7 +10422,7 @@
           <t>Post: Atlas Olive Oil Spray</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E185" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/atlas-olive-oil-spray/</t>
         </is>
@@ -10431,7 +10475,7 @@
           <t>Post: Tabanero</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E186" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/tabanero/</t>
         </is>
@@ -10484,7 +10528,7 @@
           <t>Post: YumVs</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E187" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/yumvs/</t>
         </is>
@@ -10537,7 +10581,7 @@
           <t>Post: Objet D'Art</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="E188" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/objet-dart/</t>
         </is>
@@ -10590,7 +10634,7 @@
           <t>Post: Rae Dunn</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="E189" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/rae-dunn/</t>
         </is>
@@ -10643,7 +10687,7 @@
           <t>Post: Jose Gourmet</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="E190" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/jose-gourmet/</t>
         </is>
@@ -10696,7 +10740,7 @@
           <t>Post: '73 Originals</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="E191" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/73-originals/</t>
         </is>
@@ -10749,7 +10793,7 @@
           <t>Legacy/test page: /home/</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E192" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/home/</t>
         </is>
@@ -10802,7 +10846,7 @@
           <t>Legacy/test page: /amazon-management-agency/</t>
         </is>
       </c>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="E193" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/amazon-management-agency/</t>
         </is>
@@ -10855,7 +10899,7 @@
           <t>Legacy/test page: /for-amazon-brands/</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="E194" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/for-amazon-brands/</t>
         </is>
@@ -10908,7 +10952,7 @@
           <t>Legacy/test page: /for-amazon-brandsv2/</t>
         </is>
       </c>
-      <c r="E195" s="2" t="inlineStr">
+      <c r="E195" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/for-amazon-brandsv2/</t>
         </is>
@@ -10961,7 +11005,7 @@
           <t>Legacy/test page: /amazon-growth-audit/</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="E196" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/amazon-growth-audit/</t>
         </is>
@@ -11014,7 +11058,7 @@
           <t>Legacy/test page: /amazon-growth-audit-v2/</t>
         </is>
       </c>
-      <c r="E197" s="2" t="inlineStr">
+      <c r="E197" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/amazon-growth-audit-v2/</t>
         </is>
@@ -11067,7 +11111,7 @@
           <t>Legacy/test page: /form-ads-test/</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="E198" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/form-ads-test/</t>
         </is>
@@ -11120,7 +11164,7 @@
           <t>Legacy/test page: /services/</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="E199" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/services/</t>
         </is>
@@ -11173,7 +11217,7 @@
           <t>Legacy/test page: /services-2/</t>
         </is>
       </c>
-      <c r="E200" s="2" t="inlineStr">
+      <c r="E200" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/services-2/</t>
         </is>
@@ -11226,7 +11270,7 @@
           <t>Legacy/test page: /our-service/</t>
         </is>
       </c>
-      <c r="E201" s="2" t="inlineStr">
+      <c r="E201" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/our-service/</t>
         </is>
@@ -11279,7 +11323,7 @@
           <t>Legacy/test page: /additional-services/</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr">
+      <c r="E202" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/additional-services/</t>
         </is>
@@ -11332,7 +11376,7 @@
           <t>Legacy/test page: /overview/</t>
         </is>
       </c>
-      <c r="E203" s="2" t="inlineStr">
+      <c r="E203" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/overview/</t>
         </is>
@@ -11385,7 +11429,7 @@
           <t>Legacy/test page: /marketing-division-2/</t>
         </is>
       </c>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="E204" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/marketing-division-2/</t>
         </is>
@@ -11415,7 +11459,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K204" s="2" t="inlineStr">
+      <c r="K204" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -11442,7 +11486,7 @@
           <t>Legacy/test page: /retail-management/</t>
         </is>
       </c>
-      <c r="E205" s="2" t="inlineStr">
+      <c r="E205" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/retail-management/</t>
         </is>
@@ -11472,7 +11516,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K205" s="2" t="inlineStr"/>
+      <c r="K205" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-16)</t>
+        </is>
+      </c>
       <c r="L205" s="2" t="inlineStr"/>
       <c r="M205" s="2" t="inlineStr"/>
     </row>
@@ -11495,7 +11543,7 @@
           <t>Legacy/test page: /university/</t>
         </is>
       </c>
-      <c r="E206" s="2" t="inlineStr">
+      <c r="E206" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/university/</t>
         </is>
@@ -11525,7 +11573,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K206" s="2" t="inlineStr">
+      <c r="K206" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -11552,7 +11600,7 @@
           <t>Legacy/test page: /portfolio/</t>
         </is>
       </c>
-      <c r="E207" s="2" t="inlineStr">
+      <c r="E207" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/portfolio/</t>
         </is>
@@ -11582,7 +11630,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K207" s="2" t="inlineStr">
+      <c r="K207" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -11609,7 +11657,7 @@
           <t>Legacy/test page: /recent-success/</t>
         </is>
       </c>
-      <c r="E208" s="2" t="inlineStr">
+      <c r="E208" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/recent-success/</t>
         </is>
@@ -11639,7 +11687,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K208" s="2" t="inlineStr"/>
+      <c r="K208" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-16)</t>
+        </is>
+      </c>
       <c r="L208" s="2" t="inlineStr"/>
       <c r="M208" s="2" t="inlineStr"/>
     </row>
@@ -11662,7 +11714,7 @@
           <t>Legacy/test page: /videos/</t>
         </is>
       </c>
-      <c r="E209" s="2" t="inlineStr">
+      <c r="E209" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/videos/</t>
         </is>
@@ -11692,7 +11744,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K209" s="2" t="inlineStr">
+      <c r="K209" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -11719,7 +11771,7 @@
           <t>Legacy/test page: /our-story/</t>
         </is>
       </c>
-      <c r="E210" s="2" t="inlineStr">
+      <c r="E210" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/our-story/</t>
         </is>
@@ -11749,7 +11801,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K210" s="2" t="inlineStr"/>
+      <c r="K210" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-16)</t>
+        </is>
+      </c>
       <c r="L210" s="2" t="inlineStr"/>
       <c r="M210" s="2" t="inlineStr"/>
     </row>
@@ -11772,7 +11828,7 @@
           <t>Legacy/test page: /our-team/</t>
         </is>
       </c>
-      <c r="E211" s="2" t="inlineStr">
+      <c r="E211" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/our-team/</t>
         </is>
@@ -11802,7 +11858,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K211" s="2" t="inlineStr"/>
+      <c r="K211" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-16)</t>
+        </is>
+      </c>
       <c r="L211" s="2" t="inlineStr"/>
       <c r="M211" s="2" t="inlineStr"/>
     </row>
@@ -11825,7 +11885,7 @@
           <t>Legacy/test page: /our-management/</t>
         </is>
       </c>
-      <c r="E212" s="2" t="inlineStr">
+      <c r="E212" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/our-management/</t>
         </is>
@@ -11855,7 +11915,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K212" s="2" t="inlineStr"/>
+      <c r="K212" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-16)</t>
+        </is>
+      </c>
       <c r="L212" s="2" t="inlineStr"/>
       <c r="M212" s="2" t="inlineStr"/>
     </row>
@@ -11878,7 +11942,7 @@
           <t>Legacy/test page: /our-world-wide-team/</t>
         </is>
       </c>
-      <c r="E213" s="2" t="inlineStr">
+      <c r="E213" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/our-world-wide-team/</t>
         </is>
@@ -11908,7 +11972,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K213" s="2" t="inlineStr"/>
+      <c r="K213" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-16)</t>
+        </is>
+      </c>
       <c r="L213" s="2" t="inlineStr"/>
       <c r="M213" s="2" t="inlineStr"/>
     </row>
@@ -11931,7 +11999,7 @@
           <t>Legacy/test page: /niftyone-custom-portal/</t>
         </is>
       </c>
-      <c r="E214" s="2" t="inlineStr">
+      <c r="E214" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/niftyone-custom-portal/</t>
         </is>
@@ -11961,7 +12029,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K214" s="2" t="inlineStr"/>
+      <c r="K214" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-16)</t>
+        </is>
+      </c>
       <c r="L214" s="2" t="inlineStr"/>
       <c r="M214" s="2" t="inlineStr"/>
     </row>
@@ -11984,7 +12056,7 @@
           <t>Legacy/test page: /clients/</t>
         </is>
       </c>
-      <c r="E215" s="2" t="inlineStr">
+      <c r="E215" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/clients/</t>
         </is>
@@ -12014,7 +12086,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K215" s="2" t="inlineStr">
+      <c r="K215" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -12041,7 +12113,7 @@
           <t>Legacy/test page: /lets-talk/</t>
         </is>
       </c>
-      <c r="E216" s="2" t="inlineStr">
+      <c r="E216" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/lets-talk/</t>
         </is>
@@ -12071,7 +12143,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K216" s="2" t="inlineStr">
+      <c r="K216" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -12098,7 +12170,7 @@
           <t>Legacy/test page: /book-a-call/</t>
         </is>
       </c>
-      <c r="E217" s="2" t="inlineStr">
+      <c r="E217" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/book-a-call/</t>
         </is>
@@ -12128,7 +12200,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K217" s="2" t="inlineStr">
+      <c r="K217" s="6" t="inlineStr">
         <is>
           <t>In progress (verified 2026-09-14: DevNotes from the sheet: "i set it to Non-index", confirmed live: /book-a-call/ now noindex (still 200, not merged into contact-us))</t>
         </is>
@@ -12159,7 +12231,7 @@
           <t>Legacy/test page: /thankyou/</t>
         </is>
       </c>
-      <c r="E218" s="2" t="inlineStr">
+      <c r="E218" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/thankyou/</t>
         </is>
@@ -12189,7 +12261,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K218" s="2" t="inlineStr">
+      <c r="K218" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -12216,7 +12288,7 @@
           <t>Legacy/test page: /thank-you/</t>
         </is>
       </c>
-      <c r="E219" s="2" t="inlineStr">
+      <c r="E219" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/thank-you/</t>
         </is>
@@ -12246,7 +12318,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K219" s="2" t="inlineStr">
+      <c r="K219" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -12273,7 +12345,7 @@
           <t>Legacy/test page: /test-page/</t>
         </is>
       </c>
-      <c r="E220" s="2" t="inlineStr">
+      <c r="E220" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/test-page/</t>
         </is>
@@ -12303,7 +12375,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K220" s="2" t="inlineStr">
+      <c r="K220" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -12330,7 +12402,7 @@
           <t>Legacy/test page: /test-modules/</t>
         </is>
       </c>
-      <c r="E221" s="2" t="inlineStr">
+      <c r="E221" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/test-modules/</t>
         </is>
@@ -12360,7 +12432,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K221" s="2" t="inlineStr">
+      <c r="K221" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -12387,7 +12459,7 @@
           <t>Legacy/test page: /hero/</t>
         </is>
       </c>
-      <c r="E222" s="2" t="inlineStr">
+      <c r="E222" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/hero/</t>
         </is>
@@ -12417,7 +12489,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K222" s="2" t="inlineStr">
+      <c r="K222" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -12444,7 +12516,7 @@
           <t>Legacy/test page: /sample-page/</t>
         </is>
       </c>
-      <c r="E223" s="2" t="inlineStr">
+      <c r="E223" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/sample-page/</t>
         </is>
@@ -12474,7 +12546,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K223" s="2" t="inlineStr">
+      <c r="K223" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -12501,7 +12573,7 @@
           <t>See URL</t>
         </is>
       </c>
-      <c r="E224" s="2" t="inlineStr">
+      <c r="E224" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/mastering-amazon-dsp/</t>
         </is>
@@ -12531,7 +12603,7 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="K224" s="2" t="inlineStr">
+      <c r="K224" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -12558,7 +12630,7 @@
           <t>See URL</t>
         </is>
       </c>
-      <c r="E225" s="2" t="inlineStr">
+      <c r="E225" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/subscribe-and-save-strategies/</t>
         </is>
@@ -12588,7 +12660,7 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="K225" s="2" t="inlineStr">
+      <c r="K225" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -12615,7 +12687,7 @@
           <t>See URL</t>
         </is>
       </c>
-      <c r="E226" s="2" t="inlineStr">
+      <c r="E226" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/streamlining-logistics-for-scalable-amazon-success/</t>
         </is>
@@ -12645,7 +12717,7 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="K226" s="2" t="inlineStr">
+      <c r="K226" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -12672,7 +12744,7 @@
           <t>See URL</t>
         </is>
       </c>
-      <c r="E227" s="2" t="inlineStr">
+      <c r="E227" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/</t>
         </is>
@@ -12702,7 +12774,7 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="K227" s="2" t="inlineStr">
+      <c r="K227" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14: 0 em dashes confirmed by a direct fetch of the homepage; the automated crawl that flagged this as reopened hit a screenshot timeout and returned no data for this page, not a real regression)</t>
         </is>
@@ -12729,7 +12801,7 @@
           <t>See URL</t>
         </is>
       </c>
-      <c r="E228" s="2" t="inlineStr">
+      <c r="E228" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/newsroom/</t>
         </is>
@@ -12759,7 +12831,7 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="K228" s="2" t="inlineStr">
+      <c r="K228" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -12786,7 +12858,7 @@
           <t>See URL</t>
         </is>
       </c>
-      <c r="E229" s="2" t="inlineStr">
+      <c r="E229" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/case-studies/atlas-olive-oils/</t>
         </is>
@@ -12816,7 +12888,7 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="K229" s="2" t="inlineStr">
+      <c r="K229" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -12843,7 +12915,7 @@
           <t>See URL</t>
         </is>
       </c>
-      <c r="E230" s="2" t="inlineStr">
+      <c r="E230" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/case-studies/beyoutiful/</t>
         </is>
@@ -12873,7 +12945,7 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="K230" s="2" t="inlineStr">
+      <c r="K230" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -12900,7 +12972,7 @@
           <t>See URL</t>
         </is>
       </c>
-      <c r="E231" s="2" t="inlineStr">
+      <c r="E231" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/about-us/</t>
         </is>
@@ -12930,7 +13002,7 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="K231" s="2" t="inlineStr">
+      <c r="K231" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -12957,7 +13029,7 @@
           <t>See URL</t>
         </is>
       </c>
-      <c r="E232" s="2" t="inlineStr">
+      <c r="E232" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/marketing-division-2/</t>
         </is>
@@ -12987,7 +13059,7 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="K232" s="2" t="inlineStr">
+      <c r="K232" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -13014,7 +13086,7 @@
           <t>See URL</t>
         </is>
       </c>
-      <c r="E233" s="2" t="inlineStr">
+      <c r="E233" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/marketing-devision/</t>
         </is>
@@ -13044,7 +13116,7 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="K233" s="2" t="inlineStr">
+      <c r="K233" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -13071,7 +13143,7 @@
           <t>See URL</t>
         </is>
       </c>
-      <c r="E234" s="2" t="inlineStr">
+      <c r="E234" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/retail-division/</t>
         </is>
@@ -13101,7 +13173,7 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="K234" s="2" t="inlineStr">
+      <c r="K234" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -13128,7 +13200,7 @@
           <t>See URL</t>
         </is>
       </c>
-      <c r="E235" s="2" t="inlineStr">
+      <c r="E235" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/listing-division/</t>
         </is>
@@ -13158,7 +13230,7 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="K235" s="2" t="inlineStr">
+      <c r="K235" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -13185,7 +13257,7 @@
           <t>See URL</t>
         </is>
       </c>
-      <c r="E236" s="2" t="inlineStr">
+      <c r="E236" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/case-studies/</t>
         </is>
@@ -13215,7 +13287,7 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="K236" s="2" t="inlineStr">
+      <c r="K236" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -13242,7 +13314,7 @@
           <t>See URL</t>
         </is>
       </c>
-      <c r="E237" s="2" t="inlineStr">
+      <c r="E237" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/dsp/</t>
         </is>
@@ -13272,9 +13344,9 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="K237" s="2" t="inlineStr">
-        <is>
-          <t>In progress (verified 2026-09-14: )</t>
+      <c r="K237" s="6" t="inlineStr">
+        <is>
+          <t>In progress (verified 2026-09-16)</t>
         </is>
       </c>
       <c r="L237" s="2" t="inlineStr"/>
@@ -13299,7 +13371,7 @@
           <t>See URL</t>
         </is>
       </c>
-      <c r="E238" s="2" t="inlineStr">
+      <c r="E238" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/retail-management/</t>
         </is>
@@ -13329,7 +13401,7 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="K238" s="2" t="inlineStr">
+      <c r="K238" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -13356,7 +13428,7 @@
           <t>See URL</t>
         </is>
       </c>
-      <c r="E239" s="2" t="inlineStr">
+      <c r="E239" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/clients/</t>
         </is>
@@ -13386,7 +13458,7 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="K239" s="2" t="inlineStr">
+      <c r="K239" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -13413,7 +13485,7 @@
           <t>See URL</t>
         </is>
       </c>
-      <c r="E240" s="2" t="inlineStr">
+      <c r="E240" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/videos/</t>
         </is>
@@ -13443,7 +13515,7 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="K240" s="2" t="inlineStr">
+      <c r="K240" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -13470,7 +13542,7 @@
           <t>See URL</t>
         </is>
       </c>
-      <c r="E241" s="2" t="inlineStr">
+      <c r="E241" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/case-studies/mouthwatchers/</t>
         </is>
@@ -13500,7 +13572,7 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="K241" s="2" t="inlineStr">
+      <c r="K241" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -13527,7 +13599,7 @@
           <t>New page: Brand Store Design</t>
         </is>
       </c>
-      <c r="E242" s="2" t="inlineStr">
+      <c r="E242" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/brand-store-design/</t>
         </is>
@@ -13580,7 +13652,7 @@
           <t>New page: Brand Store Design</t>
         </is>
       </c>
-      <c r="E243" s="2" t="inlineStr">
+      <c r="E243" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/brand-store-design/</t>
         </is>
@@ -13633,7 +13705,7 @@
           <t>DSM attachment category archive: ABG</t>
         </is>
       </c>
-      <c r="E244" s="2" t="inlineStr">
+      <c r="E244" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/dsm-attachment-category/abg/</t>
         </is>
@@ -13663,7 +13735,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K244" s="2" t="inlineStr">
+      <c r="K244" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -13690,7 +13762,7 @@
           <t>DSM attachment category archive: BeYoutifull</t>
         </is>
       </c>
-      <c r="E245" s="2" t="inlineStr">
+      <c r="E245" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/dsm-attachment-category/beyoutifull/</t>
         </is>
@@ -13720,7 +13792,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K245" s="2" t="inlineStr">
+      <c r="K245" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -13747,7 +13819,7 @@
           <t>DSM attachment category archive: Katjes</t>
         </is>
       </c>
-      <c r="E246" s="2" t="inlineStr">
+      <c r="E246" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/dsm-attachment-category/katjes/</t>
         </is>
@@ -13777,7 +13849,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K246" s="2" t="inlineStr">
+      <c r="K246" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -13804,7 +13876,7 @@
           <t>DSM attachment category archive: Magmod</t>
         </is>
       </c>
-      <c r="E247" s="2" t="inlineStr">
+      <c r="E247" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/dsm-attachment-category/magmod/</t>
         </is>
@@ -13834,7 +13906,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K247" s="2" t="inlineStr">
+      <c r="K247" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -13861,7 +13933,7 @@
           <t>DSM attachment category archive: Mouthwatchers</t>
         </is>
       </c>
-      <c r="E248" s="2" t="inlineStr">
+      <c r="E248" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/dsm-attachment-category/mouthwatchers/</t>
         </is>
@@ -13891,7 +13963,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K248" s="2" t="inlineStr">
+      <c r="K248" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -13918,7 +13990,7 @@
           <t>DSM attachment category archive: Rufus</t>
         </is>
       </c>
-      <c r="E249" s="2" t="inlineStr">
+      <c r="E249" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/dsm-attachment-category/rufus/</t>
         </is>
@@ -13948,7 +14020,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K249" s="2" t="inlineStr">
+      <c r="K249" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -13975,7 +14047,7 @@
           <t>DSM attachment category archive: Tabanero</t>
         </is>
       </c>
-      <c r="E250" s="2" t="inlineStr">
+      <c r="E250" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/blog/dsm-attachment-category/tabanero/</t>
         </is>
@@ -14005,7 +14077,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K250" s="2" t="inlineStr">
+      <c r="K250" s="5" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -14032,7 +14104,7 @@
           <t>About page</t>
         </is>
       </c>
-      <c r="E251" s="2" t="inlineStr">
+      <c r="E251" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/about-us/</t>
         </is>
@@ -14085,7 +14157,7 @@
           <t>About page</t>
         </is>
       </c>
-      <c r="E252" s="2" t="inlineStr">
+      <c r="E252" s="3" t="inlineStr">
         <is>
           <t>https://www.albertscott.com/about-us/</t>
         </is>
@@ -14115,12 +14187,328 @@
           <t>new</t>
         </is>
       </c>
-      <c r="K252" s="2" t="inlineStr"/>
+      <c r="K252" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-16)</t>
+        </is>
+      </c>
       <c r="L252" s="2" t="inlineStr"/>
       <c r="M252" s="2" t="inlineStr"/>
     </row>
+    <row r="253">
+      <c r="A253" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>AS-252</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>New since 2026-09-14</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>Homepage</t>
+        </is>
+      </c>
+      <c r="E253" s="3" t="inlineStr">
+        <is>
+          <t>https://www.albertscott.com/</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>A new gallery block on the homepage links every tile to the same redirecting URL</t>
+        </is>
+      </c>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t>Fetching the live homepage HTML on 2026-09-16 shows a gallery grid (class "dsm-gallery", the same Divi Supreme Modules widget behind the dsm-attachment-category taxonomy found on 2026-09-07) with at least 4 tiles, every one linking to /case-studies-2/ (a relative href), which 301s to /case-studies/. This section was not present in earlier checks; it looks like a new homepage block was added using this widget.</t>
+        </is>
+      </c>
+      <c r="H253" s="2" t="inlineStr">
+        <is>
+          <t>Point each gallery tile's link directly at https://www.albertscott.com/case-studies/, or at the specific case study each tile represents, instead of the redirecting URL.</t>
+        </is>
+      </c>
+      <c r="I253" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J253" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="K253" s="2" t="inlineStr"/>
+      <c r="L253" s="2" t="inlineStr"/>
+      <c r="M253" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M252"/>
+  <autoFilter ref="A1:M253"/>
+  <dataValidations count="1">
+    <dataValidation sqref="K2:K253" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Open,In progress,Done,Skipped"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E253" r:id="rId252"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/seo-geo/tracking/issue-tracker-for-gsheet-import.xlsx
+++ b/seo-geo/tracking/issue-tracker-for-gsheet-import.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>Open, urgent (confirmed again 2026-09-16: article still not restored, 7 days after it was found deleted)</t>
+          <t>Open, urgent (confirmed again 2026-09-17: article still not restored, 8 days since it was found deleted, and per Hassan's 2026-09-16 reply the deletion was intentional, not accidental -- see the audit note)</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr"/>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-14)</t>
+          <t>Done (verified 2026-09-17: now returns a 301 redirect to the homepage, an upgrade from the noindex it had before)</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr"/>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-14)</t>
+          <t>Done (verified 2026-09-17: now returns a 301 redirect to the homepage, an upgrade from the noindex it had before)</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr"/>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-14)</t>
+          <t>Done (verified 2026-09-17: now returns a 301 redirect to the homepage, an upgrade from the noindex it had before)</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr"/>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-14)</t>
+          <t>Done (verified 2026-09-17: now returns a 301 redirect to the homepage, an upgrade from the noindex it had before)</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr"/>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-16: source page no longer exists as a separate page, moot)</t>
+          <t>Done (verified 2026-09-17: source page no longer exists as a separate page, moot)</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr"/>

--- a/seo-geo/tracking/issue-tracker-for-gsheet-import.xlsx
+++ b/seo-geo/tracking/issue-tracker-for-gsheet-import.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Issues" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Issues'!$A$1:$M$253</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Issues'!$A$1:$M$254</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,27 +38,12 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -79,22 +64,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -463,20 +439,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M253"/>
+  <dimension ref="A1:M254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="36" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
     <col width="30" customWidth="1" min="12" max="12"/>
     <col width="30" customWidth="1" min="13" max="13"/>
   </cols>
@@ -597,7 +573,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>Open, urgent (confirmed again 2026-09-17: article still not restored, 8 days since it was found deleted, and per Hassan's 2026-09-16 reply the deletion was intentional, not accidental -- see the audit note)</t>
         </is>
@@ -654,7 +630,11 @@
           <t>R15</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-18: both Organization nodes now share @id https://www.albertscott.com/#organization, confirmed by fetching and parsing both JSON-LD blocks directly. numberOfEmployees is also now unified at 30 in both, which was not explicitly claimed but is also fixed.)</t>
+        </is>
+      </c>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr"/>
     </row>
@@ -707,7 +687,11 @@
           <t>R15</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-18: sameAs now present with LinkedIn and Crunchbase URLs, confirmed directly in the live JSON-LD.)</t>
+        </is>
+      </c>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr"/>
     </row>
@@ -813,7 +797,11 @@
           <t>G1</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>OPEN, not fixed (checked 2026-09-18: the AIOSEO schema block still declares description "E-commerce Management", unchanged, still conflicting with the homepage meta description. Do not conflate this with AS-001/AS-002 being fixed, they are related but this specific one is not done.)</t>
+        </is>
+      </c>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr"/>
     </row>
@@ -972,7 +960,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -1029,7 +1017,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -1086,7 +1074,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -1143,7 +1131,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -1200,7 +1188,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -1257,7 +1245,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -1314,7 +1302,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -1371,7 +1359,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -1428,7 +1416,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -1485,7 +1473,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -1542,7 +1530,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -1599,7 +1587,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -1656,7 +1644,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -1713,7 +1701,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -1770,7 +1758,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -1827,7 +1815,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -1884,7 +1872,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -1941,7 +1929,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -1998,7 +1986,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -2108,7 +2096,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-17: now returns a 301 redirect to the homepage, an upgrade from the noindex it had before)</t>
         </is>
@@ -2165,7 +2153,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K30" s="5" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-17: now returns a 301 redirect to the homepage, an upgrade from the noindex it had before)</t>
         </is>
@@ -2222,7 +2210,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-17: now returns a 301 redirect to the homepage, an upgrade from the noindex it had before)</t>
         </is>
@@ -2279,7 +2267,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K32" s="5" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-17: now returns a 301 redirect to the homepage, an upgrade from the noindex it had before)</t>
         </is>
@@ -2389,7 +2377,7 @@
           <t>R5</t>
         </is>
       </c>
-      <c r="K34" s="5" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -2446,7 +2434,7 @@
           <t>R5</t>
         </is>
       </c>
-      <c r="K35" s="5" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -2503,7 +2491,7 @@
           <t>R19</t>
         </is>
       </c>
-      <c r="K36" s="5" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -2560,7 +2548,7 @@
           <t>R2</t>
         </is>
       </c>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -2617,9 +2605,9 @@
           <t>R2</t>
         </is>
       </c>
-      <c r="K38" s="4" t="inlineStr">
-        <is>
-          <t>REOPENED (verified 2026-09-16: the homepage still links to https://www.albertscott.com/marketing-division/, which 301s to /marketing-devision/, confirmed by fetching the live homepage HTML directly. Not a measurement error this time; a plain absolute link on the page.)</t>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>RESOLVED, stale finding (checked 2026-09-18: /marketing-division/ is now the live, correct-spelling canonical page (200, real content, confirmed by title and H1), and the old misspelled /marketing-devision/ now 301s to it. The homepage linking to /marketing-division/ is now correct, not a bug. This tracker had the direction backwards; corrected.)</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr"/>
@@ -2674,9 +2662,9 @@
           <t>R2</t>
         </is>
       </c>
-      <c r="K39" s="4" t="inlineStr">
-        <is>
-          <t>REOPENED (verified 2026-09-16: the homepage's "Explore Logistics" button in the divisions accordion section links to /logistics-division-2/ (relative href), confirmed by fetching the live homepage HTML directly. A correct absolute link to /logistics-division/ also exists elsewhere on the page, so this looks like a second button using the old URL, not the original one being un-fixed.)</t>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>REOPENED (confirmed again 2026-09-18: the "Explore Logistics" button still links to /logistics-division-2/, which still 301s. This one is still a real, open problem, unlike AS-036.)</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr"/>
@@ -2837,7 +2825,7 @@
           <t>R2</t>
         </is>
       </c>
-      <c r="K42" s="5" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-17: source page no longer exists as a separate page, moot)</t>
         </is>
@@ -4007,7 +3995,7 @@
           <t>R8</t>
         </is>
       </c>
-      <c r="K64" s="5" t="inlineStr">
+      <c r="K64" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-16)</t>
         </is>
@@ -5071,7 +5059,7 @@
           <t>R18</t>
         </is>
       </c>
-      <c r="K84" s="5" t="inlineStr">
+      <c r="K84" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -5658,7 +5646,7 @@
           <t>R18</t>
         </is>
       </c>
-      <c r="K95" s="5" t="inlineStr">
+      <c r="K95" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -5874,7 +5862,7 @@
           <t>R8</t>
         </is>
       </c>
-      <c r="K99" s="5" t="inlineStr">
+      <c r="K99" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-16)</t>
         </is>
@@ -6037,7 +6025,7 @@
           <t>R18</t>
         </is>
       </c>
-      <c r="K102" s="5" t="inlineStr">
+      <c r="K102" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -6359,7 +6347,7 @@
           <t>R18</t>
         </is>
       </c>
-      <c r="K108" s="5" t="inlineStr">
+      <c r="K108" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -8801,7 +8789,7 @@
           <t>R20</t>
         </is>
       </c>
-      <c r="K154" s="6" t="inlineStr">
+      <c r="K154" s="2" t="inlineStr">
         <is>
           <t>In progress (verified 2026-09-14: book-a-call now noindexed; lets-talk now redirects to contact-us)</t>
         </is>
@@ -8964,7 +8952,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K157" s="5" t="inlineStr">
+      <c r="K157" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -11459,7 +11447,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K204" s="5" t="inlineStr">
+      <c r="K204" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -11516,7 +11504,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K205" s="5" t="inlineStr">
+      <c r="K205" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-16)</t>
         </is>
@@ -11573,7 +11561,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K206" s="5" t="inlineStr">
+      <c r="K206" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -11630,7 +11618,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K207" s="5" t="inlineStr">
+      <c r="K207" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -11687,7 +11675,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K208" s="5" t="inlineStr">
+      <c r="K208" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-16)</t>
         </is>
@@ -11744,7 +11732,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K209" s="5" t="inlineStr">
+      <c r="K209" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -11801,7 +11789,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K210" s="5" t="inlineStr">
+      <c r="K210" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-16)</t>
         </is>
@@ -11858,7 +11846,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K211" s="5" t="inlineStr">
+      <c r="K211" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-16)</t>
         </is>
@@ -11915,7 +11903,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K212" s="5" t="inlineStr">
+      <c r="K212" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-16)</t>
         </is>
@@ -11972,7 +11960,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K213" s="5" t="inlineStr">
+      <c r="K213" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-16)</t>
         </is>
@@ -12029,7 +12017,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K214" s="5" t="inlineStr">
+      <c r="K214" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-16)</t>
         </is>
@@ -12086,7 +12074,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K215" s="5" t="inlineStr">
+      <c r="K215" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -12143,7 +12131,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K216" s="5" t="inlineStr">
+      <c r="K216" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -12200,7 +12188,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K217" s="6" t="inlineStr">
+      <c r="K217" s="2" t="inlineStr">
         <is>
           <t>In progress (verified 2026-09-14: DevNotes from the sheet: "i set it to Non-index", confirmed live: /book-a-call/ now noindex (still 200, not merged into contact-us))</t>
         </is>
@@ -12261,7 +12249,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K218" s="5" t="inlineStr">
+      <c r="K218" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -12318,7 +12306,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K219" s="5" t="inlineStr">
+      <c r="K219" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -12375,7 +12363,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K220" s="5" t="inlineStr">
+      <c r="K220" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -12432,7 +12420,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K221" s="5" t="inlineStr">
+      <c r="K221" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -12489,7 +12477,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K222" s="5" t="inlineStr">
+      <c r="K222" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -12546,7 +12534,7 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K223" s="5" t="inlineStr">
+      <c r="K223" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -12603,7 +12591,7 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="K224" s="5" t="inlineStr">
+      <c r="K224" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -12660,7 +12648,7 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="K225" s="5" t="inlineStr">
+      <c r="K225" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -12717,7 +12705,7 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="K226" s="5" t="inlineStr">
+      <c r="K226" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -12774,7 +12762,7 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="K227" s="5" t="inlineStr">
+      <c r="K227" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14: 0 em dashes confirmed by a direct fetch of the homepage; the automated crawl that flagged this as reopened hit a screenshot timeout and returned no data for this page, not a real regression)</t>
         </is>
@@ -12831,7 +12819,7 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="K228" s="5" t="inlineStr">
+      <c r="K228" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -12888,7 +12876,7 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="K229" s="5" t="inlineStr">
+      <c r="K229" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -12945,7 +12933,7 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="K230" s="5" t="inlineStr">
+      <c r="K230" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -13002,7 +12990,7 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="K231" s="5" t="inlineStr">
+      <c r="K231" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -13059,7 +13047,7 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="K232" s="5" t="inlineStr">
+      <c r="K232" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -13116,7 +13104,7 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="K233" s="5" t="inlineStr">
+      <c r="K233" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -13173,7 +13161,7 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="K234" s="5" t="inlineStr">
+      <c r="K234" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -13230,7 +13218,7 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="K235" s="5" t="inlineStr">
+      <c r="K235" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -13287,7 +13275,7 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="K236" s="5" t="inlineStr">
+      <c r="K236" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -13344,7 +13332,7 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="K237" s="6" t="inlineStr">
+      <c r="K237" s="2" t="inlineStr">
         <is>
           <t>In progress (verified 2026-09-16)</t>
         </is>
@@ -13401,7 +13389,7 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="K238" s="5" t="inlineStr">
+      <c r="K238" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -13458,7 +13446,7 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="K239" s="5" t="inlineStr">
+      <c r="K239" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -13515,7 +13503,7 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="K240" s="5" t="inlineStr">
+      <c r="K240" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -13572,7 +13560,7 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="K241" s="5" t="inlineStr">
+      <c r="K241" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -13735,7 +13723,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K244" s="5" t="inlineStr">
+      <c r="K244" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -13792,7 +13780,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K245" s="5" t="inlineStr">
+      <c r="K245" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -13849,7 +13837,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K246" s="5" t="inlineStr">
+      <c r="K246" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -13906,7 +13894,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K247" s="5" t="inlineStr">
+      <c r="K247" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -13963,7 +13951,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K248" s="5" t="inlineStr">
+      <c r="K248" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -14020,7 +14008,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K249" s="5" t="inlineStr">
+      <c r="K249" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -14077,7 +14065,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="K250" s="5" t="inlineStr">
+      <c r="K250" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-14)</t>
         </is>
@@ -14187,7 +14175,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="K252" s="5" t="inlineStr">
+      <c r="K252" s="2" t="inlineStr">
         <is>
           <t>Done (verified 2026-09-16)</t>
         </is>
@@ -14248,10 +14236,63 @@
       <c r="L253" s="2" t="inlineStr"/>
       <c r="M253" s="2" t="inlineStr"/>
     </row>
+    <row r="254">
+      <c r="A254" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>AS-253</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>New since 2026-09-17</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>Legacy services page</t>
+        </is>
+      </c>
+      <c r="E254" s="3" t="inlineStr">
+        <is>
+          <t>https://www.albertscott.com/services/</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>A live pricing figure (9% commission) is exposed inside broken shortcode text on an indexable page</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
+          <t>Fetching /services/ directly on 2026-09-18 shows raw, unrendered Visual Composer shortcode text on screen and in the meta description, exactly as flagged elsewhere (AS-197). Within that shortcode text, the literal strings "9% Commission" and "9% Service" appear, a real pricing figure, visible to any visitor and any crawler. The same shortcode-broken pattern is confirmed still live on /our-service/ (AS-199), /overview/ (AS-201), and /additional-services/ (AS-200) as well; none contain a comparable pricing figure on inspection today. This is the same set of pages Hassan gave as his justification for deleting AS-000 (shortcode-broken content), which is still live and unaddressed while AS-000 was removed.</t>
+        </is>
+      </c>
+      <c r="H254" s="2" t="inlineStr">
+        <is>
+          <t>Treat this with more urgency than the general legacy-page cleanup: confirm with Yoni whether this pricing figure is current or stale before doing anything else, then redirect or rebuild the page per the existing AS-197 recommendation.</t>
+        </is>
+      </c>
+      <c r="I254" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J254" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="K254" s="2" t="inlineStr"/>
+      <c r="L254" s="2" t="inlineStr"/>
+      <c r="M254" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M253"/>
+  <autoFilter ref="A1:M254"/>
   <dataValidations count="1">
-    <dataValidation sqref="K2:K253" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K254" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Skipped"</formula1>
     </dataValidation>
   </dataValidations>
@@ -14508,6 +14549,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E251" r:id="rId250"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E252" r:id="rId251"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E254" r:id="rId253"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/seo-geo/tracking/issue-tracker-for-gsheet-import.xlsx
+++ b/seo-geo/tracking/issue-tracker-for-gsheet-import.xlsx
@@ -3942,7 +3942,11 @@
           <t>R3</t>
         </is>
       </c>
-      <c r="K63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-21: live title tag now reads "Marketing division - Albert Scott" (correct spelling) and the AIOSEO breadcrumb schema no longer says "Devision". https://www.albertscott.com/marketing-division/ is now the canonical 200 page; https://www.albertscott.com/marketing-devision/ 301s to it. Note: one sitewide nav menu link still points at the old /marketing-devision/ URL, which still works via the redirect but adds an unnecessary hop; minor, not blocking this row.)</t>
+        </is>
+      </c>
       <c r="L63" s="2" t="inlineStr"/>
       <c r="M63" s="2" t="inlineStr"/>
     </row>
@@ -9645,7 +9649,11 @@
           <t>R13</t>
         </is>
       </c>
-      <c r="K170" s="2" t="inlineStr"/>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-21: https://www.albertscott.com/project/national-public-seatinf/ now 301s to the corrected slug https://www.albertscott.com/project/national-public-seating/.)</t>
+        </is>
+      </c>
       <c r="L170" s="2" t="inlineStr"/>
       <c r="M170" s="2" t="inlineStr"/>
     </row>
@@ -10334,7 +10342,11 @@
           <t>R13</t>
         </is>
       </c>
-      <c r="K183" s="2" t="inlineStr"/>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-21: same fix as AS-168, confirmed by direct request, 301 to the corrected slug.)</t>
+        </is>
+      </c>
       <c r="L183" s="2" t="inlineStr"/>
       <c r="M183" s="2" t="inlineStr"/>
     </row>
@@ -10387,7 +10399,11 @@
           <t>R12</t>
         </is>
       </c>
-      <c r="K184" s="2" t="inlineStr"/>
+      <c r="K184" s="2" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-21: https://www.albertscott.com/blog/mouthwatchers/ now 301s to https://www.albertscott.com/case-studies/mouthwatchers/, exactly the recommended fix.)</t>
+        </is>
+      </c>
       <c r="L184" s="2" t="inlineStr"/>
       <c r="M184" s="2" t="inlineStr"/>
     </row>
@@ -10811,7 +10827,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K192" s="2" t="inlineStr"/>
+      <c r="K192" s="2" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-21: https://www.albertscott.com/home/ now 301s to https://www.albertscott.com/.)</t>
+        </is>
+      </c>
       <c r="L192" s="2" t="inlineStr"/>
       <c r="M192" s="2" t="inlineStr"/>
     </row>
@@ -10864,7 +10884,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K193" s="2" t="inlineStr"/>
+      <c r="K193" s="2" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-21: https://www.albertscott.com/amazon-management-agency/ now 301s to https://www.albertscott.com/.)</t>
+        </is>
+      </c>
       <c r="L193" s="2" t="inlineStr"/>
       <c r="M193" s="2" t="inlineStr"/>
     </row>
@@ -10917,7 +10941,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K194" s="2" t="inlineStr"/>
+      <c r="K194" s="2" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-21: https://www.albertscott.com/for-amazon-brands/ now carries meta robots "noindex, nofollow...". Page still returns 200 but is out of the index, matching the recommended fix for an active ad landing page.)</t>
+        </is>
+      </c>
       <c r="L194" s="2" t="inlineStr"/>
       <c r="M194" s="2" t="inlineStr"/>
     </row>
@@ -10970,7 +10998,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K195" s="2" t="inlineStr"/>
+      <c r="K195" s="2" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-21: https://www.albertscott.com/for-amazon-brandsv2/ now carries the same noindex robots tag.)</t>
+        </is>
+      </c>
       <c r="L195" s="2" t="inlineStr"/>
       <c r="M195" s="2" t="inlineStr"/>
     </row>
@@ -11023,7 +11055,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K196" s="2" t="inlineStr"/>
+      <c r="K196" s="2" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-21: https://www.albertscott.com/amazon-growth-audit/ now carries the same noindex robots tag.)</t>
+        </is>
+      </c>
       <c r="L196" s="2" t="inlineStr"/>
       <c r="M196" s="2" t="inlineStr"/>
     </row>
@@ -11076,7 +11112,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K197" s="2" t="inlineStr"/>
+      <c r="K197" s="2" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-21: https://www.albertscott.com/amazon-growth-audit-v2/ now returns 404, functionally the same outcome as the recommended delete/410.)</t>
+        </is>
+      </c>
       <c r="L197" s="2" t="inlineStr"/>
       <c r="M197" s="2" t="inlineStr"/>
     </row>
@@ -11129,7 +11169,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K198" s="2" t="inlineStr"/>
+      <c r="K198" s="2" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-21: https://www.albertscott.com/form-ads-test/ now returns 404.)</t>
+        </is>
+      </c>
       <c r="L198" s="2" t="inlineStr"/>
       <c r="M198" s="2" t="inlineStr"/>
     </row>
@@ -11182,7 +11226,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K199" s="2" t="inlineStr"/>
+      <c r="K199" s="2" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-21: https://www.albertscott.com/services/ now 301s to https://www.albertscott.com/. This also resolves AS-253, the pricing figure that was exposed in this page's broken shortcode text; that content is no longer served.)</t>
+        </is>
+      </c>
       <c r="L199" s="2" t="inlineStr"/>
       <c r="M199" s="2" t="inlineStr"/>
     </row>
@@ -11235,7 +11283,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K200" s="2" t="inlineStr"/>
+      <c r="K200" s="2" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-21: https://www.albertscott.com/services-2/ now 301s to https://www.albertscott.com/.)</t>
+        </is>
+      </c>
       <c r="L200" s="2" t="inlineStr"/>
       <c r="M200" s="2" t="inlineStr"/>
     </row>
@@ -11288,7 +11340,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K201" s="2" t="inlineStr"/>
+      <c r="K201" s="2" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-21: https://www.albertscott.com/our-service/ now 301s to https://www.albertscott.com/.)</t>
+        </is>
+      </c>
       <c r="L201" s="2" t="inlineStr"/>
       <c r="M201" s="2" t="inlineStr"/>
     </row>
@@ -11341,7 +11397,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K202" s="2" t="inlineStr"/>
+      <c r="K202" s="2" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-21: https://www.albertscott.com/additional-services/ now 301s to https://www.albertscott.com/.)</t>
+        </is>
+      </c>
       <c r="L202" s="2" t="inlineStr"/>
       <c r="M202" s="2" t="inlineStr"/>
     </row>
@@ -11394,7 +11454,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="K203" s="2" t="inlineStr"/>
+      <c r="K203" s="2" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-21: https://www.albertscott.com/overview/ now 301s to https://www.albertscott.com/.)</t>
+        </is>
+      </c>
       <c r="L203" s="2" t="inlineStr"/>
       <c r="M203" s="2" t="inlineStr"/>
     </row>
@@ -14122,7 +14186,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="K251" s="2" t="inlineStr"/>
+      <c r="K251" s="2" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-21: /about-us/ now has a "Our Story" section reading "Albert Scott was founded in 2020 by David Greenblatt and Shlomo Greenblatt after seeing firsthand how difficult it had become for brands to succeed on Amazon...". The founding story is present, and the page grew from 648 to 721 words to hold it.)</t>
+        </is>
+      </c>
       <c r="L251" s="2" t="inlineStr"/>
       <c r="M251" s="2" t="inlineStr"/>
     </row>
@@ -14285,7 +14353,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="K254" s="2" t="inlineStr"/>
+      <c r="K254" s="2" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-21: /services/ now 301s to the homepage instead of serving the broken shortcode page, so the "9% Commission" pricing text is no longer exposed. Resolved as a side effect of the AS-197 redirect.)</t>
+        </is>
+      </c>
       <c r="L254" s="2" t="inlineStr"/>
       <c r="M254" s="2" t="inlineStr"/>
     </row>
